--- a/Team-Data/2008-09/12-11-2008-09.xlsx
+++ b/Team-Data/2008-09/12-11-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -757,7 +824,7 @@
         <v>22</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
         <v>16</v>
@@ -769,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
         <v>27</v>
@@ -778,7 +845,7 @@
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR2" t="n">
         <v>23</v>
@@ -787,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>16</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
@@ -808,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
         <v>19</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -858,70 +925,70 @@
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>36.5</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.478</v>
+        <v>0.473</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="M3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.365</v>
+        <v>0.352</v>
       </c>
       <c r="O3" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="P3" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.763</v>
       </c>
       <c r="R3" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T3" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="U3" t="n">
-        <v>22</v>
+        <v>21.3</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.6</v>
+        <v>100.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,13 +1003,13 @@
         <v>9</v>
       </c>
       <c r="AI3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL3" t="n">
         <v>17</v>
@@ -951,7 +1018,7 @@
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
         <v>3</v>
@@ -960,31 +1027,31 @@
         <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
         <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AZ3" t="n">
         <v>24</v>
@@ -993,10 +1060,10 @@
         <v>3</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -1025,97 +1092,97 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.304</v>
+        <v>0.318</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>32.8</v>
+        <v>32.5</v>
       </c>
       <c r="J4" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.437</v>
+        <v>0.434</v>
       </c>
       <c r="L4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M4" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.358</v>
+        <v>0.363</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="P4" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="n">
         <v>10.8</v>
       </c>
       <c r="S4" t="n">
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="T4" t="n">
-        <v>37.8</v>
+        <v>37.5</v>
       </c>
       <c r="U4" t="n">
         <v>18.1</v>
       </c>
       <c r="V4" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="X4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z4" t="n">
         <v>22.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="AB4" t="n">
         <v>89.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.1</v>
+        <v>-4</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,25 +1191,25 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AM4" t="n">
         <v>24</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AR4" t="n">
         <v>18</v>
@@ -1157,10 +1224,10 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>23</v>
@@ -1172,13 +1239,13 @@
         <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>0.45</v>
+        <v>0.476</v>
       </c>
       <c r="H5" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I5" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.436</v>
+        <v>0.439</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O5" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.803</v>
+        <v>0.799</v>
       </c>
       <c r="R5" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="T5" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U5" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="V5" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W5" t="n">
         <v>8.300000000000001</v>
@@ -1270,43 +1337,43 @@
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI5" t="n">
         <v>12</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>18</v>
@@ -1315,16 +1382,16 @@
         <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR5" t="n">
         <v>10</v>
@@ -1336,10 +1403,10 @@
         <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>6</v>
@@ -1348,19 +1415,19 @@
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ5" t="n">
         <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -1389,91 +1456,91 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.905</v>
+        <v>0.864</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.8</v>
+        <v>38.4</v>
       </c>
       <c r="J6" t="n">
-        <v>80.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.485</v>
+        <v>0.482</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M6" t="n">
+        <v>20</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="O6" t="n">
         <v>20.3</v>
       </c>
-      <c r="N6" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="O6" t="n">
-        <v>20.1</v>
-      </c>
       <c r="P6" t="n">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
       <c r="R6" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="S6" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T6" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U6" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="V6" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>104.8</v>
+        <v>103.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
@@ -1482,34 +1549,34 @@
         <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
         <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" t="n">
         <v>9</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>10</v>
       </c>
       <c r="AQ6" t="n">
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
         <v>9</v>
@@ -1521,25 +1588,25 @@
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
         <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.571</v>
+        <v>0.55</v>
       </c>
       <c r="H7" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I7" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="J7" t="n">
-        <v>84.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0.451</v>
@@ -1601,70 +1668,70 @@
         <v>19.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.334</v>
+        <v>0.331</v>
       </c>
       <c r="O7" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P7" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S7" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="T7" t="n">
-        <v>46.2</v>
+        <v>46.6</v>
       </c>
       <c r="U7" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="V7" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.4</v>
+        <v>19.9</v>
       </c>
       <c r="AA7" t="n">
         <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.1</v>
+        <v>101.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AF7" t="n">
         <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ7" t="n">
         <v>4</v>
@@ -1682,10 +1749,10 @@
         <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ7" t="n">
         <v>6</v>
@@ -1700,28 +1767,28 @@
         <v>1</v>
       </c>
       <c r="AU7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV7" t="n">
         <v>11</v>
       </c>
-      <c r="AV7" t="n">
-        <v>8</v>
-      </c>
       <c r="AW7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX7" t="n">
         <v>15</v>
       </c>
-      <c r="AX7" t="n">
-        <v>18</v>
-      </c>
       <c r="AY7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA7" t="n">
         <v>26</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
         <v>11</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>5.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1846,7 +1913,7 @@
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ8" t="n">
         <v>24</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>24</v>
@@ -1885,13 +1952,13 @@
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW8" t="n">
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
         <v>27</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-0.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF9" t="n">
         <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
         <v>24</v>
@@ -2031,58 +2098,58 @@
         <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
         <v>14</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
         <v>25</v>
       </c>
       <c r="AN9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
         <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
         <v>21</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
         <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
         <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-4.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
@@ -2210,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
         <v>2</v>
@@ -2219,7 +2286,7 @@
         <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>15</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
@@ -2270,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>3.8</v>
       </c>
       <c r="AD11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE11" t="n">
         <v>7</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>8</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
@@ -2401,7 +2468,7 @@
         <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM11" t="n">
         <v>12</v>
@@ -2413,7 +2480,7 @@
         <v>5</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
@@ -2431,10 +2498,10 @@
         <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
@@ -2446,7 +2513,7 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB11" t="n">
         <v>22</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
         <v>6</v>
@@ -2589,7 +2656,7 @@
         <v>7</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>28</v>
@@ -2634,7 +2701,7 @@
         <v>12</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-6.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI13" t="n">
         <v>20</v>
@@ -2765,7 +2832,7 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM13" t="n">
         <v>17</v>
@@ -2783,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
         <v>22</v>
@@ -2795,10 +2862,10 @@
         <v>21</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0.85</v>
+        <v>0.857</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="J14" t="n">
-        <v>84.8</v>
+        <v>84.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2872,64 +2939,64 @@
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>0.37</v>
+        <v>0.378</v>
       </c>
       <c r="O14" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="P14" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.761</v>
+        <v>0.764</v>
       </c>
       <c r="R14" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="S14" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="T14" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
         <v>14.7</v>
       </c>
       <c r="W14" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>109</v>
+        <v>108.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
         <v>3</v>
@@ -2944,7 +3011,7 @@
         <v>5</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
@@ -2953,22 +3020,22 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT14" t="n">
         <v>2</v>
@@ -2986,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ14" t="n">
         <v>8</v>
@@ -2998,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-5.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG15" t="n">
         <v>23</v>
@@ -3150,7 +3217,7 @@
         <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT15" t="n">
         <v>27</v>
@@ -3168,19 +3235,19 @@
         <v>26</v>
       </c>
       <c r="AY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA15" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9</v>
       </c>
       <c r="BB15" t="n">
         <v>26</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>1.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3299,19 +3366,19 @@
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI16" t="n">
         <v>11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM16" t="n">
         <v>8</v>
@@ -3323,19 +3390,19 @@
         <v>22</v>
       </c>
       <c r="AP16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU16" t="n">
         <v>19</v>
@@ -3344,19 +3411,19 @@
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -3391,43 +3458,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17" t="n">
         <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.391</v>
+        <v>0.375</v>
       </c>
       <c r="H17" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I17" t="n">
         <v>35.7</v>
       </c>
       <c r="J17" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.431</v>
+        <v>0.433</v>
       </c>
       <c r="L17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
         <v>14.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="O17" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="P17" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="Q17" t="n">
         <v>0.76</v>
@@ -3436,46 +3503,46 @@
         <v>13.5</v>
       </c>
       <c r="S17" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="U17" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V17" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="W17" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y17" t="n">
         <v>5.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="AB17" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.1</v>
+        <v>-3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
         <v>21</v>
@@ -3484,7 +3551,7 @@
         <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
@@ -3499,13 +3566,13 @@
         <v>26</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>19</v>
@@ -3514,7 +3581,7 @@
         <v>2</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
         <v>5</v>
@@ -3526,7 +3593,7 @@
         <v>29</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX17" t="n">
         <v>28</v>
@@ -3538,7 +3605,7 @@
         <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
@@ -3663,13 +3730,13 @@
         <v>28</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3687,22 +3754,22 @@
         <v>17</v>
       </c>
       <c r="AP18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
         <v>17</v>
       </c>
       <c r="AU18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
         <v>12</v>
@@ -3711,7 +3778,7 @@
         <v>29</v>
       </c>
       <c r="AX18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY18" t="n">
         <v>28</v>
@@ -3720,7 +3787,7 @@
         <v>26</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>24</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -3833,28 +3900,28 @@
         <v>-1.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF19" t="n">
         <v>10</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
       </c>
       <c r="AI19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>15</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>16</v>
-      </c>
       <c r="AK19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL19" t="n">
         <v>6</v>
@@ -3872,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
         <v>19</v>
@@ -3881,7 +3948,7 @@
         <v>19</v>
       </c>
       <c r="AT19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="n">
         <v>27</v>
@@ -3893,7 +3960,7 @@
         <v>26</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
         <v>14</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
         <v>26</v>
@@ -4066,10 +4133,10 @@
         <v>28</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
         <v>7</v>
@@ -4084,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-3</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
         <v>17</v>
@@ -4206,13 +4273,13 @@
         <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH21" t="n">
         <v>15</v>
       </c>
       <c r="AI21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
@@ -4236,7 +4303,7 @@
         <v>27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4260,16 +4327,16 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA21" t="n">
         <v>30</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4464,7 @@
         <v>28</v>
       </c>
       <c r="AJ22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK22" t="n">
         <v>30</v>
@@ -4412,7 +4479,7 @@
         <v>7</v>
       </c>
       <c r="AO22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP22" t="n">
         <v>13</v>
@@ -4433,13 +4500,13 @@
         <v>25</v>
       </c>
       <c r="AV22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW22" t="n">
         <v>18</v>
       </c>
       <c r="AX22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>5.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4591,13 +4658,13 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO23" t="n">
         <v>8</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4612,7 +4679,7 @@
         <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>-1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
@@ -4758,10 +4825,10 @@
         <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
         <v>25</v>
@@ -4782,7 +4849,7 @@
         <v>20</v>
       </c>
       <c r="AQ24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR24" t="n">
         <v>1</v>
@@ -4794,7 +4861,7 @@
         <v>3</v>
       </c>
       <c r="AU24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -4934,10 +5001,10 @@
         <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
         <v>8</v>
@@ -4961,7 +5028,7 @@
         <v>11</v>
       </c>
       <c r="AP25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ25" t="n">
         <v>28</v>
@@ -4982,16 +5049,16 @@
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -5044,31 +5111,31 @@
         <v>48.2</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="L26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.397</v>
+        <v>0.408</v>
       </c>
       <c r="O26" t="n">
-        <v>17.6</v>
+        <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.776</v>
+        <v>0.772</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
@@ -5080,31 +5147,31 @@
         <v>41</v>
       </c>
       <c r="U26" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="V26" t="n">
         <v>13.2</v>
       </c>
       <c r="W26" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X26" t="n">
         <v>5.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AD26" t="n">
         <v>2</v>
@@ -5119,31 +5186,31 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>4</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ26" t="n">
         <v>10</v>
@@ -5158,13 +5225,13 @@
         <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX26" t="n">
         <v>10</v>
@@ -5173,13 +5240,13 @@
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-7.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
         <v>26</v>
@@ -5310,7 +5377,7 @@
         <v>14</v>
       </c>
       <c r="AK27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL27" t="n">
         <v>24</v>
@@ -5322,10 +5389,10 @@
         <v>30</v>
       </c>
       <c r="AO27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ27" t="n">
         <v>9</v>
@@ -5343,7 +5410,7 @@
         <v>18</v>
       </c>
       <c r="AV27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
         <v>9</v>
@@ -5480,7 +5547,7 @@
         <v>7</v>
       </c>
       <c r="AG28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5498,7 +5565,7 @@
         <v>5</v>
       </c>
       <c r="AM28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN28" t="n">
         <v>4</v>
@@ -5522,7 +5589,7 @@
         <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
         <v>3</v>
@@ -5534,7 +5601,7 @@
         <v>29</v>
       </c>
       <c r="AY28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>-4.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF29" t="n">
         <v>18</v>
@@ -5668,10 +5735,10 @@
         <v>8</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
         <v>17</v>
@@ -5686,10 +5753,10 @@
         <v>5</v>
       </c>
       <c r="AO29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,7 +5765,7 @@
         <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>29</v>
@@ -5728,7 +5795,7 @@
         <v>20</v>
       </c>
       <c r="BC29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -5757,94 +5824,94 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F30" t="n">
         <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>0.625</v>
+        <v>0.609</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J30" t="n">
-        <v>78.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.481</v>
       </c>
       <c r="L30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O30" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
       <c r="R30" t="n">
         <v>11.7</v>
       </c>
       <c r="S30" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T30" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U30" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="V30" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="W30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z30" t="n">
         <v>22.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
         <v>10</v>
       </c>
       <c r="AG30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5853,7 +5920,7 @@
         <v>7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK30" t="n">
         <v>3</v>
@@ -5865,16 +5932,16 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
         <v>11</v>
@@ -5889,22 +5956,22 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ30" t="n">
         <v>19</v>
       </c>
       <c r="BA30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
@@ -5939,91 +6006,91 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>0.211</v>
       </c>
       <c r="H31" t="n">
         <v>48.3</v>
       </c>
       <c r="I31" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>82.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M31" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>0.317</v>
+        <v>0.322</v>
       </c>
       <c r="O31" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P31" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
       <c r="R31" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S31" t="n">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="T31" t="n">
-        <v>39.8</v>
+        <v>40.5</v>
       </c>
       <c r="U31" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="V31" t="n">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="W31" t="n">
         <v>7.8</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5.4</v>
+        <v>-3.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE31" t="n">
         <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG31" t="n">
         <v>27</v>
@@ -6035,10 +6102,10 @@
         <v>10</v>
       </c>
       <c r="AJ31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL31" t="n">
         <v>19</v>
@@ -6050,28 +6117,28 @@
         <v>25</v>
       </c>
       <c r="AO31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP31" t="n">
         <v>19</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>18</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>17</v>
-      </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AT31" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW31" t="n">
         <v>10</v>
@@ -6080,19 +6147,19 @@
         <v>22</v>
       </c>
       <c r="AY31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC31" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-11-2008-09</t>
+          <t>2008-12-11</t>
         </is>
       </c>
     </row>
